--- a/tsne/results_tsne.xlsx
+++ b/tsne/results_tsne.xlsx
@@ -452,10 +452,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-10.19667339324951</v>
+        <v>-3.402727603912354</v>
       </c>
       <c r="B2" t="n">
-        <v>13.8878345489502</v>
+        <v>15.78973770141602</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -470,10 +470,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-10.3390645980835</v>
+        <v>-3.380010604858398</v>
       </c>
       <c r="B3" t="n">
-        <v>14.02145862579346</v>
+        <v>16.00537300109863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -488,10 +488,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-10.36535263061523</v>
+        <v>-3.377109050750732</v>
       </c>
       <c r="B4" t="n">
-        <v>14.04608154296875</v>
+        <v>16.04485130310059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-10.53367137908936</v>
+        <v>-3.361441373825073</v>
       </c>
       <c r="B5" t="n">
-        <v>14.18999671936035</v>
+        <v>16.29544639587402</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -524,10 +524,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-10.928147315979</v>
+        <v>-3.341637849807739</v>
       </c>
       <c r="B6" t="n">
-        <v>14.51790618896484</v>
+        <v>16.85801696777344</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-11.03532981872559</v>
+        <v>-3.335959672927856</v>
       </c>
       <c r="B7" t="n">
-        <v>14.60799121856689</v>
+        <v>17.0045051574707</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -560,10 +560,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4.058512687683105</v>
+        <v>-9.738709449768066</v>
       </c>
       <c r="B8" t="n">
-        <v>-7.270299434661865</v>
+        <v>-4.856927394866943</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -578,10 +578,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4.046692848205566</v>
+        <v>-9.736640930175781</v>
       </c>
       <c r="B9" t="n">
-        <v>-7.261211395263672</v>
+        <v>-4.871575355529785</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -596,10 +596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4.010813236236572</v>
+        <v>-9.730295181274414</v>
       </c>
       <c r="B10" t="n">
-        <v>-7.223462581634521</v>
+        <v>-4.921181201934814</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.994414448738098</v>
+        <v>-6.881583213806152</v>
       </c>
       <c r="B11" t="n">
-        <v>-9.243014335632324</v>
+        <v>-6.18736743927002</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -632,10 +632,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1.850719571113586</v>
+        <v>-7.013858795166016</v>
       </c>
       <c r="B12" t="n">
-        <v>-9.048585891723633</v>
+        <v>-6.411858558654785</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -650,10 +650,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1.687882781028748</v>
+        <v>-7.222263813018799</v>
       </c>
       <c r="B13" t="n">
-        <v>-8.781445503234863</v>
+        <v>-6.69445276260376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1.602153539657593</v>
+        <v>-7.479094982147217</v>
       </c>
       <c r="B14" t="n">
-        <v>-8.482654571533203</v>
+        <v>-6.935609340667725</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -686,10 +686,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.557566285133362</v>
+        <v>-7.67003870010376</v>
       </c>
       <c r="B15" t="n">
-        <v>-8.28875732421875</v>
+        <v>-7.070553302764893</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1.499998092651367</v>
+        <v>-8.067691802978516</v>
       </c>
       <c r="B16" t="n">
-        <v>-7.870582580566406</v>
+        <v>-7.346222877502441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1.51594066619873</v>
+        <v>-8.124162673950195</v>
       </c>
       <c r="B17" t="n">
-        <v>-7.830524921417236</v>
+        <v>-7.344476222991943</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1.707858920097351</v>
+        <v>-8.468599319458008</v>
       </c>
       <c r="B18" t="n">
-        <v>-7.511875629425049</v>
+        <v>-7.391953468322754</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -758,10 +758,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1.417696237564087</v>
+        <v>-8.68825626373291</v>
       </c>
       <c r="B19" t="n">
-        <v>-7.181746959686279</v>
+        <v>-7.827713012695312</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1.43550169467926</v>
+        <v>-8.705761909484863</v>
       </c>
       <c r="B20" t="n">
-        <v>-7.152344703674316</v>
+        <v>-7.83843994140625</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2.286836385726929</v>
+        <v>-7.281073570251465</v>
       </c>
       <c r="B21" t="n">
-        <v>-8.990767478942871</v>
+        <v>-6.018412590026855</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2.313618183135986</v>
+        <v>-7.550876140594482</v>
       </c>
       <c r="B22" t="n">
-        <v>-8.718161582946777</v>
+        <v>-6.146460056304932</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2.300596237182617</v>
+        <v>-7.672103404998779</v>
       </c>
       <c r="B23" t="n">
-        <v>-8.595237731933594</v>
+        <v>-6.209685802459717</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -848,10 +848,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2.269694805145264</v>
+        <v>-7.85108470916748</v>
       </c>
       <c r="B24" t="n">
-        <v>-8.387258529663086</v>
+        <v>-6.344142436981201</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -866,10 +866,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2.205504417419434</v>
+        <v>-8.056015968322754</v>
       </c>
       <c r="B25" t="n">
-        <v>-8.16041374206543</v>
+        <v>-6.521305084228516</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2.071183204650879</v>
+        <v>-8.416080474853516</v>
       </c>
       <c r="B26" t="n">
-        <v>-7.74919319152832</v>
+        <v>-6.874569892883301</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-6.189032077789307</v>
+        <v>5.372172832489014</v>
       </c>
       <c r="B27" t="n">
-        <v>21.3336124420166</v>
+        <v>19.42431259155273</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -920,10 +920,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-6.294394016265869</v>
+        <v>5.300468444824219</v>
       </c>
       <c r="B28" t="n">
-        <v>21.3699951171875</v>
+        <v>19.52518272399902</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -938,10 +938,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-6.383855819702148</v>
+        <v>5.237287521362305</v>
       </c>
       <c r="B29" t="n">
-        <v>21.40158462524414</v>
+        <v>19.61432075500488</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -956,10 +956,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-6.556880950927734</v>
+        <v>5.11454439163208</v>
       </c>
       <c r="B30" t="n">
-        <v>21.45912742614746</v>
+        <v>19.78720474243164</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -974,10 +974,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-6.79164981842041</v>
+        <v>4.953558444976807</v>
       </c>
       <c r="B31" t="n">
-        <v>21.53557014465332</v>
+        <v>20.00725555419922</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -992,10 +992,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.5158891677856445</v>
+        <v>-6.552989482879639</v>
       </c>
       <c r="B32" t="n">
-        <v>-2.970651149749756</v>
+        <v>-0.8559256792068481</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1.023791909217834</v>
+        <v>-6.344451427459717</v>
       </c>
       <c r="B33" t="n">
-        <v>-3.521778106689453</v>
+        <v>-1.673206567764282</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1.572840332984924</v>
+        <v>-6.107766628265381</v>
       </c>
       <c r="B34" t="n">
-        <v>-4.152464389801025</v>
+        <v>-2.572720766067505</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1.668423056602478</v>
+        <v>-6.017929077148438</v>
       </c>
       <c r="B35" t="n">
-        <v>-4.177966117858887</v>
+        <v>-2.654990911483765</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1.708014726638794</v>
+        <v>-5.98734712600708</v>
       </c>
       <c r="B36" t="n">
-        <v>-4.18196439743042</v>
+        <v>-2.684375047683716</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>13.17440700531006</v>
+        <v>7.405078887939453</v>
       </c>
       <c r="B37" t="n">
-        <v>-2.087526798248291</v>
+        <v>-6.007045745849609</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>12.82698822021484</v>
+        <v>7.037396907806396</v>
       </c>
       <c r="B38" t="n">
-        <v>-2.010562896728516</v>
+        <v>-5.914887428283691</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>12.21094608306885</v>
+        <v>6.381523609161377</v>
       </c>
       <c r="B39" t="n">
-        <v>-1.832097411155701</v>
+        <v>-5.709442138671875</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>11.50758171081543</v>
+        <v>5.642007827758789</v>
       </c>
       <c r="B40" t="n">
-        <v>-1.583990216255188</v>
+        <v>-5.439056396484375</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>11.05288028717041</v>
+        <v>5.133832931518555</v>
       </c>
       <c r="B41" t="n">
-        <v>-1.414734721183777</v>
+        <v>-5.322482585906982</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10.61472320556641</v>
+        <v>4.70923376083374</v>
       </c>
       <c r="B42" t="n">
-        <v>-1.224892854690552</v>
+        <v>-5.005268096923828</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.06608544290065765</v>
+        <v>-6.700116157531738</v>
       </c>
       <c r="B43" t="n">
-        <v>-2.524848937988281</v>
+        <v>-0.1605735272169113</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.2344448119401932</v>
+        <v>-6.658005237579346</v>
       </c>
       <c r="B44" t="n">
-        <v>-2.709180116653442</v>
+        <v>-0.4272877871990204</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.4661509096622467</v>
+        <v>-6.578215599060059</v>
       </c>
       <c r="B45" t="n">
-        <v>-2.964945077896118</v>
+        <v>-0.8100643157958984</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.9702069163322449</v>
+        <v>-6.366705417633057</v>
       </c>
       <c r="B46" t="n">
-        <v>-3.507299184799194</v>
+        <v>-1.617286682128906</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1.542361617088318</v>
+        <v>-6.129470348358154</v>
       </c>
       <c r="B47" t="n">
-        <v>-4.164093971252441</v>
+        <v>-2.558797836303711</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.0657573863863945</v>
+        <v>-6.700116157531738</v>
       </c>
       <c r="B48" t="n">
-        <v>-2.524945020675659</v>
+        <v>-0.1605735272169113</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.4661509096622467</v>
+        <v>-6.578215599060059</v>
       </c>
       <c r="B49" t="n">
-        <v>-2.964945077896118</v>
+        <v>-0.8100643157958984</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.9702069163322449</v>
+        <v>-6.36286449432373</v>
       </c>
       <c r="B50" t="n">
-        <v>-3.507299184799194</v>
+        <v>-1.618037581443787</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1334,10 +1334,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1.540387988090515</v>
+        <v>-6.129470348358154</v>
       </c>
       <c r="B51" t="n">
-        <v>-4.165393829345703</v>
+        <v>-2.558797836303711</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>13.96005725860596</v>
+        <v>6.09311580657959</v>
       </c>
       <c r="B52" t="n">
-        <v>-10.90005397796631</v>
+        <v>-15.23208045959473</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>13.77046298980713</v>
+        <v>5.862895965576172</v>
       </c>
       <c r="B53" t="n">
-        <v>-10.95829105377197</v>
+        <v>-15.26033782958984</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>14.17686557769775</v>
+        <v>6.331194877624512</v>
       </c>
       <c r="B54" t="n">
-        <v>-11.00614643096924</v>
+        <v>-15.47703838348389</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1406,10 +1406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>14.00208854675293</v>
+        <v>6.123229503631592</v>
       </c>
       <c r="B55" t="n">
-        <v>-11.02690982818604</v>
+        <v>-15.49804401397705</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>13.79011917114258</v>
+        <v>5.843079566955566</v>
       </c>
       <c r="B56" t="n">
-        <v>-11.0516242980957</v>
+        <v>-15.42000198364258</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>14.17686557769775</v>
+        <v>6.331194877624512</v>
       </c>
       <c r="B57" t="n">
-        <v>-11.00614643096924</v>
+        <v>-15.47703838348389</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>14.00208854675293</v>
+        <v>6.123229503631592</v>
       </c>
       <c r="B58" t="n">
-        <v>-11.02690982818604</v>
+        <v>-15.49804401397705</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>13.79011917114258</v>
+        <v>5.843079566955566</v>
       </c>
       <c r="B59" t="n">
-        <v>-11.0516242980957</v>
+        <v>-15.42000198364258</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>12.69034576416016</v>
+        <v>6.891180992126465</v>
       </c>
       <c r="B60" t="n">
-        <v>-1.970871686935425</v>
+        <v>-5.865106105804443</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>11.86013031005859</v>
+        <v>6.01807975769043</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.70490038394928</v>
+        <v>-5.55455207824707</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1532,10 +1532,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>11.0738468170166</v>
+        <v>5.221245288848877</v>
       </c>
       <c r="B62" t="n">
-        <v>-1.389177680015564</v>
+        <v>-5.146873950958252</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1550,10 +1550,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>10.57082939147949</v>
+        <v>4.671176910400391</v>
       </c>
       <c r="B63" t="n">
-        <v>-1.203636527061462</v>
+        <v>-4.96138858795166</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>12.6905460357666</v>
+        <v>6.891180992126465</v>
       </c>
       <c r="B64" t="n">
-        <v>-1.97076427936554</v>
+        <v>-5.865106105804443</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>11.86013031005859</v>
+        <v>6.01807975769043</v>
       </c>
       <c r="B65" t="n">
-        <v>-1.70490038394928</v>
+        <v>-5.55455207824707</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>11.07411956787109</v>
+        <v>5.221245288848877</v>
       </c>
       <c r="B66" t="n">
-        <v>-1.38820207118988</v>
+        <v>-5.146873950958252</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>10.57082939147949</v>
+        <v>4.671176910400391</v>
       </c>
       <c r="B67" t="n">
-        <v>-1.203636527061462</v>
+        <v>-4.96138858795166</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>14.67366695404053</v>
+        <v>7.275599002838135</v>
       </c>
       <c r="B68" t="n">
-        <v>-9.331647872924805</v>
+        <v>-13.91766166687012</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>14.50708770751953</v>
+        <v>7.101783275604248</v>
       </c>
       <c r="B69" t="n">
-        <v>-9.083911895751953</v>
+        <v>-13.56435680389404</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>14.66897964477539</v>
+        <v>7.27507495880127</v>
       </c>
       <c r="B70" t="n">
-        <v>-9.323494911193848</v>
+        <v>-13.9089183807373</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>14.50271701812744</v>
+        <v>7.103044986724854</v>
       </c>
       <c r="B71" t="n">
-        <v>-9.073107719421387</v>
+        <v>-13.55277729034424</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>14.66897964477539</v>
+        <v>7.27507495880127</v>
       </c>
       <c r="B72" t="n">
-        <v>-9.323494911193848</v>
+        <v>-13.9089183807373</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>14.50271701812744</v>
+        <v>7.103044986724854</v>
       </c>
       <c r="B73" t="n">
-        <v>-9.073107719421387</v>
+        <v>-13.55277729034424</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-5.599414348602295</v>
+        <v>2.513256072998047</v>
       </c>
       <c r="B74" t="n">
-        <v>16.21598243713379</v>
+        <v>14.82776546478271</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-5.619373798370361</v>
+        <v>2.508819580078125</v>
       </c>
       <c r="B75" t="n">
-        <v>16.23055076599121</v>
+        <v>14.85228443145752</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-6.218286037445068</v>
+        <v>2.402204036712646</v>
       </c>
       <c r="B76" t="n">
-        <v>16.85502433776855</v>
+        <v>15.75259590148926</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-6.246893405914307</v>
+        <v>2.388840198516846</v>
       </c>
       <c r="B77" t="n">
-        <v>16.87293434143066</v>
+        <v>15.78681945800781</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1820,10 +1820,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-6.295722007751465</v>
+        <v>2.362598419189453</v>
       </c>
       <c r="B78" t="n">
-        <v>16.89935111999512</v>
+        <v>15.84136199951172</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-6.97735071182251</v>
+        <v>2.363805055618286</v>
       </c>
       <c r="B79" t="n">
-        <v>17.78876113891602</v>
+        <v>16.99650955200195</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-6.969565868377686</v>
+        <v>2.346264123916626</v>
       </c>
       <c r="B80" t="n">
-        <v>17.75149726867676</v>
+        <v>16.96096611022949</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-8.129951477050781</v>
+        <v>-15.62815189361572</v>
       </c>
       <c r="B81" t="n">
-        <v>-4.342285633087158</v>
+        <v>2.630383729934692</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-7.922118663787842</v>
+        <v>-15.46173095703125</v>
       </c>
       <c r="B82" t="n">
-        <v>-4.562282562255859</v>
+        <v>2.451202869415283</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-7.565273761749268</v>
+        <v>-15.07879734039307</v>
       </c>
       <c r="B83" t="n">
-        <v>-4.318016529083252</v>
+        <v>2.297966718673706</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1928,10 +1928,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-7.218024730682373</v>
+        <v>-15.31122970581055</v>
       </c>
       <c r="B84" t="n">
-        <v>-4.362362384796143</v>
+        <v>1.701895117759705</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-7.044905662536621</v>
+        <v>-14.64441299438477</v>
       </c>
       <c r="B85" t="n">
-        <v>-4.908550262451172</v>
+        <v>1.778449892997742</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1964,10 +1964,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-6.729806423187256</v>
+        <v>-14.89909172058105</v>
       </c>
       <c r="B86" t="n">
-        <v>-4.95862340927124</v>
+        <v>1.172117829322815</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-6.300878524780273</v>
+        <v>-14.29046630859375</v>
       </c>
       <c r="B87" t="n">
-        <v>-4.612100601196289</v>
+        <v>1.207168221473694</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2000,10 +2000,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-6.087417125701904</v>
+        <v>-14.34663867950439</v>
       </c>
       <c r="B88" t="n">
-        <v>-4.864799499511719</v>
+        <v>0.7919958829879761</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-7.922118663787842</v>
+        <v>-15.64277458190918</v>
       </c>
       <c r="B89" t="n">
-        <v>-4.562282562255859</v>
+        <v>2.266137361526489</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-7.565273761749268</v>
+        <v>-15.07877445220947</v>
       </c>
       <c r="B90" t="n">
-        <v>-4.318016529083252</v>
+        <v>2.29797887802124</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-7.355021953582764</v>
+        <v>-15.31019401550293</v>
       </c>
       <c r="B91" t="n">
-        <v>-4.864595413208008</v>
+        <v>1.701105237007141</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-6.901343822479248</v>
+        <v>-14.64441299438477</v>
       </c>
       <c r="B92" t="n">
-        <v>-4.406434535980225</v>
+        <v>1.778449892997742</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2090,10 +2090,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-6.592372894287109</v>
+        <v>-14.90021324157715</v>
       </c>
       <c r="B93" t="n">
-        <v>-4.476795196533203</v>
+        <v>1.172014236450195</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-6.410471439361572</v>
+        <v>-14.29046726226807</v>
       </c>
       <c r="B94" t="n">
-        <v>-4.973752975463867</v>
+        <v>1.207168459892273</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-6.087421894073486</v>
+        <v>-14.34451580047607</v>
       </c>
       <c r="B95" t="n">
-        <v>-4.864815711975098</v>
+        <v>0.7927258014678955</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-7.497774124145508</v>
+        <v>-13.12729167938232</v>
       </c>
       <c r="B96" t="n">
-        <v>-1.767693400382996</v>
+        <v>4.522667407989502</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-7.105430603027344</v>
+        <v>-13.20186519622803</v>
       </c>
       <c r="B97" t="n">
-        <v>-1.447380185127258</v>
+        <v>4.048511028289795</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-6.917374134063721</v>
+        <v>-12.53738975524902</v>
       </c>
       <c r="B98" t="n">
-        <v>-2.008297920227051</v>
+        <v>4.129256725311279</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-6.466808319091797</v>
+        <v>-12.79944133758545</v>
       </c>
       <c r="B99" t="n">
-        <v>-1.528582096099854</v>
+        <v>3.525380611419678</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -2216,10 +2216,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-6.315489292144775</v>
+        <v>-12.15059185028076</v>
       </c>
       <c r="B100" t="n">
-        <v>-2.142733097076416</v>
+        <v>3.543652772903442</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-5.900157451629639</v>
+        <v>-12.39318752288818</v>
       </c>
       <c r="B101" t="n">
-        <v>-1.836341619491577</v>
+        <v>2.999229907989502</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>-5.723197460174561</v>
+        <v>-12.07639217376709</v>
       </c>
       <c r="B102" t="n">
-        <v>-2.224010944366455</v>
+        <v>2.822696447372437</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>-7.720498085021973</v>
+        <v>-13.51690673828125</v>
       </c>
       <c r="B103" t="n">
-        <v>-1.696816563606262</v>
+        <v>4.54136323928833</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>-7.497774124145508</v>
+        <v>-13.12729167938232</v>
       </c>
       <c r="B104" t="n">
-        <v>-1.767693400382996</v>
+        <v>4.522667407989502</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2306,10 +2306,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>-7.105430603027344</v>
+        <v>-13.20186519622803</v>
       </c>
       <c r="B105" t="n">
-        <v>-1.447380185127258</v>
+        <v>4.048511028289795</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>-6.917364120483398</v>
+        <v>-12.53738975524902</v>
       </c>
       <c r="B106" t="n">
-        <v>-2.007773876190186</v>
+        <v>4.129256725311279</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-6.466933727264404</v>
+        <v>-12.79967975616455</v>
       </c>
       <c r="B107" t="n">
-        <v>-1.528290271759033</v>
+        <v>3.525745153427124</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>-6.315411567687988</v>
+        <v>-12.15059185028076</v>
       </c>
       <c r="B108" t="n">
-        <v>-2.143512964248657</v>
+        <v>3.543652772903442</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-5.900157451629639</v>
+        <v>-12.4052906036377</v>
       </c>
       <c r="B109" t="n">
-        <v>-1.836341619491577</v>
+        <v>2.994085311889648</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>-5.723020076751709</v>
+        <v>-12.07639217376709</v>
       </c>
       <c r="B110" t="n">
-        <v>-2.222872972488403</v>
+        <v>2.822696447372437</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>-3.156245946884155</v>
+        <v>-8.22358226776123</v>
       </c>
       <c r="B111" t="n">
-        <v>-0.3986214399337769</v>
+        <v>2.736793041229248</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-3.070268630981445</v>
+        <v>-8.355198860168457</v>
       </c>
       <c r="B112" t="n">
-        <v>-0.4823822379112244</v>
+        <v>2.579756736755371</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>-3.111361026763916</v>
+        <v>-8.021293640136719</v>
       </c>
       <c r="B113" t="n">
-        <v>-0.7530684471130371</v>
+        <v>2.418447732925415</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2468,10 +2468,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-2.814066886901855</v>
+        <v>-8.365930557250977</v>
       </c>
       <c r="B114" t="n">
-        <v>-0.7737846374511719</v>
+        <v>2.157626628875732</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2486,10 +2486,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-2.809972286224365</v>
+        <v>-8.13617992401123</v>
       </c>
       <c r="B115" t="n">
-        <v>-0.9528572559356689</v>
+        <v>2.020122051239014</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-3.07032322883606</v>
+        <v>-8.35537052154541</v>
       </c>
       <c r="B116" t="n">
-        <v>-0.4823594391345978</v>
+        <v>2.579676151275635</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-3.111506700515747</v>
+        <v>-8.021306991577148</v>
       </c>
       <c r="B117" t="n">
-        <v>-0.7532386183738708</v>
+        <v>2.418415546417236</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-2.81389594078064</v>
+        <v>-8.365930557250977</v>
       </c>
       <c r="B118" t="n">
-        <v>-0.773533821105957</v>
+        <v>2.157626628875732</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>-2.809827089309692</v>
+        <v>-8.13617992401123</v>
       </c>
       <c r="B119" t="n">
-        <v>-0.9527599811553955</v>
+        <v>2.020122051239014</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-9.784656524658203</v>
+        <v>-13.05208492279053</v>
       </c>
       <c r="B120" t="n">
-        <v>0.5153283476829529</v>
+        <v>7.270720481872559</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-9.77755069732666</v>
+        <v>-13.0702543258667</v>
       </c>
       <c r="B121" t="n">
-        <v>0.5119677186012268</v>
+        <v>7.282339572906494</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -2612,10 +2612,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>-9.771618843078613</v>
+        <v>-13.08745574951172</v>
       </c>
       <c r="B122" t="n">
-        <v>0.5272465348243713</v>
+        <v>7.287142753601074</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>-9.77755069732666</v>
+        <v>-13.0702543258667</v>
       </c>
       <c r="B123" t="n">
-        <v>0.5119677186012268</v>
+        <v>7.282339572906494</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>-9.771618843078613</v>
+        <v>-13.08732604980469</v>
       </c>
       <c r="B124" t="n">
-        <v>0.5272465348243713</v>
+        <v>7.286635875701904</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>-8.415615081787109</v>
+        <v>-9.781437873840332</v>
       </c>
       <c r="B125" t="n">
-        <v>2.947358846664429</v>
+        <v>6.788848400115967</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2684,10 +2684,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>-8.190874099731445</v>
+        <v>-9.823260307312012</v>
       </c>
       <c r="B126" t="n">
-        <v>2.776946783065796</v>
+        <v>6.45647668838501</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -2702,10 +2702,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>-7.939762592315674</v>
+        <v>-9.861876487731934</v>
       </c>
       <c r="B127" t="n">
-        <v>2.621284008026123</v>
+        <v>6.127871513366699</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>-8.415918350219727</v>
+        <v>-9.781437873840332</v>
       </c>
       <c r="B128" t="n">
-        <v>2.947672367095947</v>
+        <v>6.788848400115967</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>-8.190874099731445</v>
+        <v>-9.823260307312012</v>
       </c>
       <c r="B129" t="n">
-        <v>2.776946783065796</v>
+        <v>6.45647668838501</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>-7.939762592315674</v>
+        <v>-9.859614372253418</v>
       </c>
       <c r="B130" t="n">
-        <v>2.621284008026123</v>
+        <v>6.124044895172119</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>-7.814930438995361</v>
+        <v>-8.716907501220703</v>
       </c>
       <c r="B131" t="n">
-        <v>3.653990507125854</v>
+        <v>6.517915725708008</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -2792,10 +2792,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>-7.565956115722656</v>
+        <v>-8.72087574005127</v>
       </c>
       <c r="B132" t="n">
-        <v>3.50619101524353</v>
+        <v>6.181826114654541</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -2810,10 +2810,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>-7.377447128295898</v>
+        <v>-8.765734672546387</v>
       </c>
       <c r="B133" t="n">
-        <v>3.361763477325439</v>
+        <v>5.909411907196045</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -2828,10 +2828,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>-7.816771984100342</v>
+        <v>-8.716907501220703</v>
       </c>
       <c r="B134" t="n">
-        <v>3.655284404754639</v>
+        <v>6.517915725708008</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>-7.564291000366211</v>
+        <v>-8.729527473449707</v>
       </c>
       <c r="B135" t="n">
-        <v>3.504249572753906</v>
+        <v>6.173133373260498</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -2864,10 +2864,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>-7.378037452697754</v>
+        <v>-8.765734672546387</v>
       </c>
       <c r="B136" t="n">
-        <v>3.363247871398926</v>
+        <v>5.909411907196045</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>-2.307515859603882</v>
+        <v>-5.885695934295654</v>
       </c>
       <c r="B137" t="n">
-        <v>-25.61770248413086</v>
+        <v>-24.9383373260498</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>-1.961840033531189</v>
+        <v>-6.318732738494873</v>
       </c>
       <c r="B138" t="n">
-        <v>-25.74328422546387</v>
+        <v>-24.84602355957031</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>-1.628392815589905</v>
+        <v>-6.618175029754639</v>
       </c>
       <c r="B139" t="n">
-        <v>-25.24017715454102</v>
+        <v>-24.29221153259277</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>-1.245733618736267</v>
+        <v>-7.200128555297852</v>
       </c>
       <c r="B140" t="n">
-        <v>-25.68298530578613</v>
+        <v>-24.36661148071289</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2954,10 +2954,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>-0.870415210723877</v>
+        <v>-7.792328834533691</v>
       </c>
       <c r="B141" t="n">
-        <v>-25.23147583007812</v>
+        <v>-24.2707691192627</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>-0.4697437286376953</v>
+        <v>-8.210921287536621</v>
       </c>
       <c r="B142" t="n">
-        <v>-25.50871467590332</v>
+        <v>-23.96325492858887</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>-0.07968262583017349</v>
+        <v>-8.656431198120117</v>
       </c>
       <c r="B143" t="n">
-        <v>-25.34771919250488</v>
+        <v>-23.52682495117188</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>-2.602223873138428</v>
+        <v>-5.488723278045654</v>
       </c>
       <c r="B144" t="n">
-        <v>-25.49486923217773</v>
+        <v>-24.88218307495117</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>-2.359319925308228</v>
+        <v>-5.701580047607422</v>
       </c>
       <c r="B145" t="n">
-        <v>-25.37435531616211</v>
+        <v>-24.55643653869629</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>-2.03348445892334</v>
+        <v>-6.13433313369751</v>
       </c>
       <c r="B146" t="n">
-        <v>-25.22967338562012</v>
+        <v>-24.40875625610352</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -3062,10 +3062,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>-1.664656400680542</v>
+        <v>-6.743842601776123</v>
       </c>
       <c r="B147" t="n">
-        <v>-25.25168991088867</v>
+        <v>-24.6864013671875</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -3080,10 +3080,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>-1.245733618736267</v>
+        <v>-7.200128555297852</v>
       </c>
       <c r="B148" t="n">
-        <v>-25.68298530578613</v>
+        <v>-24.36661148071289</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -3098,10 +3098,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>-0.8828656673431396</v>
+        <v>-7.630990028381348</v>
       </c>
       <c r="B149" t="n">
-        <v>-25.22749328613281</v>
+        <v>-23.99445915222168</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -3116,10 +3116,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>-0.5152026414871216</v>
+        <v>-8.075748443603516</v>
       </c>
       <c r="B150" t="n">
-        <v>-25.62715911865234</v>
+        <v>-23.83198928833008</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -3134,10 +3134,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>-0.1968716681003571</v>
+        <v>-8.508922576904297</v>
       </c>
       <c r="B151" t="n">
-        <v>-25.32727813720703</v>
+        <v>-23.63186454772949</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>-10.06363582611084</v>
+        <v>0.5305458903312683</v>
       </c>
       <c r="B152" t="n">
-        <v>-25.57570648193359</v>
+        <v>-30.48196220397949</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>-9.904465675354004</v>
+        <v>-0.006245700176805258</v>
       </c>
       <c r="B153" t="n">
-        <v>-25.14870071411133</v>
+        <v>-30.52987480163574</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>-9.690224647521973</v>
+        <v>-0.5315636396408081</v>
       </c>
       <c r="B154" t="n">
-        <v>-24.75446701049805</v>
+        <v>-30.51655769348145</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -3206,10 +3206,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>-9.565345764160156</v>
+        <v>-1.027641773223877</v>
       </c>
       <c r="B155" t="n">
-        <v>-24.34196090698242</v>
+        <v>-30.5815486907959</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>-9.203264236450195</v>
+        <v>-1.538899421691895</v>
       </c>
       <c r="B156" t="n">
-        <v>-24.04335784912109</v>
+        <v>-30.23831748962402</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>-9.138821601867676</v>
+        <v>-1.922877430915833</v>
       </c>
       <c r="B157" t="n">
-        <v>-23.73032760620117</v>
+        <v>-30.36420059204102</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>-10.18631458282471</v>
+        <v>0.9463905096054077</v>
       </c>
       <c r="B158" t="n">
-        <v>-25.87440872192383</v>
+        <v>-30.4218807220459</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>-10.06054973602295</v>
+        <v>0.5215690135955811</v>
       </c>
       <c r="B159" t="n">
-        <v>-25.56948089599609</v>
+        <v>-30.48323059082031</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -3296,10 +3296,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>-9.907379150390625</v>
+        <v>0.002956036478281021</v>
       </c>
       <c r="B160" t="n">
-        <v>-25.15489196777344</v>
+        <v>-30.51359367370605</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>-9.655447006225586</v>
+        <v>-0.5204968452453613</v>
       </c>
       <c r="B161" t="n">
-        <v>-24.78236961364746</v>
+        <v>-30.42074966430664</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>-9.354899406433105</v>
+        <v>-1.049989581108093</v>
       </c>
       <c r="B162" t="n">
-        <v>-24.42510795593262</v>
+        <v>-30.32682800292969</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>-9.202910423278809</v>
+        <v>-1.498077511787415</v>
       </c>
       <c r="B163" t="n">
-        <v>-24.04352378845215</v>
+        <v>-30.52298736572266</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>-9.204286575317383</v>
+        <v>-1.742392778396606</v>
       </c>
       <c r="B164" t="n">
-        <v>-23.86976623535156</v>
+        <v>-30.32146263122559</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -3386,10 +3386,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>-1.732868194580078</v>
+        <v>-5.537017345428467</v>
       </c>
       <c r="B165" t="n">
-        <v>-22.54649353027344</v>
+        <v>-22.47652816772461</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -3404,10 +3404,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>-1.151771187782288</v>
+        <v>-6.341232299804688</v>
       </c>
       <c r="B166" t="n">
-        <v>-22.86291885375977</v>
+        <v>-22.46893119812012</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -3422,10 +3422,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>-1.007800102233887</v>
+        <v>-6.091031551361084</v>
       </c>
       <c r="B167" t="n">
-        <v>-23.11166763305664</v>
+        <v>-21.82945251464844</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>-0.6021049618721008</v>
+        <v>-6.702882766723633</v>
       </c>
       <c r="B168" t="n">
-        <v>-23.16412925720215</v>
+        <v>-21.75732040405273</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -3458,10 +3458,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>-0.3707870244979858</v>
+        <v>-7.261148452758789</v>
       </c>
       <c r="B169" t="n">
-        <v>-21.97458267211914</v>
+        <v>-22.21661758422852</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>0.03238338232040405</v>
+        <v>-7.39130973815918</v>
       </c>
       <c r="B170" t="n">
-        <v>-22.68621063232422</v>
+        <v>-21.32834434509277</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>0.3239994943141937</v>
+        <v>-7.975680351257324</v>
       </c>
       <c r="B171" t="n">
-        <v>-22.05789375305176</v>
+        <v>-22.00857353210449</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -3512,10 +3512,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>0.7469488382339478</v>
+        <v>-8.397289276123047</v>
       </c>
       <c r="B172" t="n">
-        <v>-22.61808204650879</v>
+        <v>-21.49518585205078</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>-1.737501621246338</v>
+        <v>-5.623434543609619</v>
       </c>
       <c r="B173" t="n">
-        <v>-22.83438301086426</v>
+        <v>-22.68086814880371</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -3548,10 +3548,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>-1.445429563522339</v>
+        <v>-5.69124174118042</v>
       </c>
       <c r="B174" t="n">
-        <v>-22.22399520874023</v>
+        <v>-21.99271202087402</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>-1.070249676704407</v>
+        <v>-6.508851528167725</v>
       </c>
       <c r="B175" t="n">
-        <v>-22.37666130065918</v>
+        <v>-22.47171783447266</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>-0.7411121726036072</v>
+        <v>-6.431900024414062</v>
       </c>
       <c r="B176" t="n">
-        <v>-21.96357917785645</v>
+        <v>-21.3823070526123</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>-0.3641662001609802</v>
+        <v>-6.782894611358643</v>
       </c>
       <c r="B177" t="n">
-        <v>-22.89499282836914</v>
+        <v>-21.11432647705078</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -3620,10 +3620,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>-0.03259991854429245</v>
+        <v>-7.39130973815918</v>
       </c>
       <c r="B178" t="n">
-        <v>-21.94519996643066</v>
+        <v>-21.32834434509277</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>0.3712545335292816</v>
+        <v>-7.782681941986084</v>
       </c>
       <c r="B179" t="n">
-        <v>-23.1897144317627</v>
+        <v>-20.9467601776123</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>0.7314125895500183</v>
+        <v>-8.250123023986816</v>
       </c>
       <c r="B180" t="n">
-        <v>-22.91744995117188</v>
+        <v>-21.19478034973145</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>-1.341028928756714</v>
+        <v>-6.090149879455566</v>
       </c>
       <c r="B181" t="n">
-        <v>-23.05777168273926</v>
+        <v>-22.56673812866211</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -3692,10 +3692,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>-1.055376768112183</v>
+        <v>-6.068843841552734</v>
       </c>
       <c r="B182" t="n">
-        <v>-22.03078079223633</v>
+        <v>-21.60623741149902</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>-0.5459823608398438</v>
+        <v>-6.942651748657227</v>
       </c>
       <c r="B183" t="n">
-        <v>-22.51669692993164</v>
+        <v>-22.11206245422363</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -3728,10 +3728,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>-0.2472058236598969</v>
+        <v>-7.34691333770752</v>
       </c>
       <c r="B184" t="n">
-        <v>-23.23359680175781</v>
+        <v>-22.18580436706543</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>0.01768858917057514</v>
+        <v>-7.39130973815918</v>
       </c>
       <c r="B185" t="n">
-        <v>-22.40676879882812</v>
+        <v>-21.32834434509277</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -3764,10 +3764,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>0.2988598346710205</v>
+        <v>-7.961176872253418</v>
       </c>
       <c r="B186" t="n">
-        <v>-23.22227096557617</v>
+        <v>-22.01301956176758</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>0.6915351748466492</v>
+        <v>-8.472134590148926</v>
       </c>
       <c r="B187" t="n">
-        <v>-22.27852439880371</v>
+        <v>-21.85519599914551</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>-8.559072494506836</v>
+        <v>0.3453590869903564</v>
       </c>
       <c r="B188" t="n">
-        <v>-26.3496036529541</v>
+        <v>-29.30256271362305</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -3818,10 +3818,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>-8.312743186950684</v>
+        <v>-0.2701177299022675</v>
       </c>
       <c r="B189" t="n">
-        <v>-25.87807083129883</v>
+        <v>-29.19597053527832</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -3836,10 +3836,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>-8.066539764404297</v>
+        <v>-0.854369044303894</v>
       </c>
       <c r="B190" t="n">
-        <v>-25.46879959106445</v>
+        <v>-29.11447334289551</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -3854,10 +3854,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>-8.706455230712891</v>
+        <v>0.3653308749198914</v>
       </c>
       <c r="B191" t="n">
-        <v>-26.22996711730957</v>
+        <v>-29.03642463684082</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -3872,10 +3872,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>-8.364888191223145</v>
+        <v>-0.2625219821929932</v>
       </c>
       <c r="B192" t="n">
-        <v>-25.8461971282959</v>
+        <v>-29.21018600463867</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>-8.070221900939941</v>
+        <v>-0.8436605334281921</v>
       </c>
       <c r="B193" t="n">
-        <v>-25.47469902038574</v>
+        <v>-29.1119556427002</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>-9.172636032104492</v>
+        <v>1.184412121772766</v>
       </c>
       <c r="B194" t="n">
-        <v>-26.75706672668457</v>
+        <v>-29.49703407287598</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -3926,10 +3926,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>-8.96277904510498</v>
+        <v>0.8514180183410645</v>
       </c>
       <c r="B195" t="n">
-        <v>-26.55452919006348</v>
+        <v>-29.36030197143555</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>-8.710108757019043</v>
+        <v>0.3574837148189545</v>
       </c>
       <c r="B196" t="n">
-        <v>-26.23839569091797</v>
+        <v>-29.29926300048828</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -3962,10 +3962,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>-8.228019714355469</v>
+        <v>-0.2203451097011566</v>
       </c>
       <c r="B197" t="n">
-        <v>-25.97700881958008</v>
+        <v>-28.93701362609863</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>-7.997387409210205</v>
+        <v>-1.048959612846375</v>
       </c>
       <c r="B198" t="n">
-        <v>-25.35883903503418</v>
+        <v>-29.13876152038574</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -3998,10 +3998,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>12.75636577606201</v>
+        <v>5.880288600921631</v>
       </c>
       <c r="B199" t="n">
-        <v>-6.881873607635498</v>
+        <v>-10.88975143432617</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>12.74586772918701</v>
+        <v>5.877918720245361</v>
       </c>
       <c r="B200" t="n">
-        <v>-6.851279735565186</v>
+        <v>-10.85396766662598</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -4034,10 +4034,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>12.73233795166016</v>
+        <v>5.873442649841309</v>
       </c>
       <c r="B201" t="n">
-        <v>-6.823651790618896</v>
+        <v>-10.82349109649658</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>12.64747333526611</v>
+        <v>5.966835498809814</v>
       </c>
       <c r="B202" t="n">
-        <v>-6.3466477394104</v>
+        <v>-10.27781295776367</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>12.6381721496582</v>
+        <v>5.960843563079834</v>
       </c>
       <c r="B203" t="n">
-        <v>-6.308878421783447</v>
+        <v>-10.23634052276611</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>12.6197509765625</v>
+        <v>5.956302165985107</v>
       </c>
       <c r="B204" t="n">
-        <v>-6.252886772155762</v>
+        <v>-10.17440128326416</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>-9.762337684631348</v>
+        <v>-0.07494873553514481</v>
       </c>
       <c r="B205" t="n">
-        <v>17.54343795776367</v>
+        <v>18.55327796936035</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -4124,10 +4124,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>-10.38037872314453</v>
+        <v>-0.5475029945373535</v>
       </c>
       <c r="B206" t="n">
-        <v>17.59472846984863</v>
+        <v>18.99606323242188</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -4142,10 +4142,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>-10.95700168609619</v>
+        <v>-0.9830833077430725</v>
       </c>
       <c r="B207" t="n">
-        <v>17.64908218383789</v>
+        <v>19.40828323364258</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -4160,10 +4160,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>-11.53056526184082</v>
+        <v>-1.395357728004456</v>
       </c>
       <c r="B208" t="n">
-        <v>17.75219917297363</v>
+        <v>19.87644004821777</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -4178,10 +4178,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>-12.34237861633301</v>
+        <v>-1.873012185096741</v>
       </c>
       <c r="B209" t="n">
-        <v>18.01241111755371</v>
+        <v>20.61618423461914</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -4196,10 +4196,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>-12.82893085479736</v>
+        <v>-2.102579116821289</v>
       </c>
       <c r="B210" t="n">
-        <v>18.26861190795898</v>
+        <v>21.14109992980957</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -4214,10 +4214,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>-9.631263732910156</v>
+        <v>0.6301491856575012</v>
       </c>
       <c r="B211" t="n">
-        <v>18.45524406433105</v>
+        <v>19.21582412719727</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>-9.967094421386719</v>
+        <v>0.3822581470012665</v>
       </c>
       <c r="B212" t="n">
-        <v>18.51013946533203</v>
+        <v>19.47885894775391</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>-10.52926921844482</v>
+        <v>-0.007632583379745483</v>
       </c>
       <c r="B213" t="n">
-        <v>18.61705780029297</v>
+        <v>19.92861175537109</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -4268,10 +4268,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>-10.82324600219727</v>
+        <v>-0.2057533413171768</v>
       </c>
       <c r="B214" t="n">
-        <v>18.68549728393555</v>
+        <v>20.17786979675293</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -4286,10 +4286,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>-11.52125835418701</v>
+        <v>-0.6377002596855164</v>
       </c>
       <c r="B215" t="n">
-        <v>18.89247131347656</v>
+        <v>20.79995155334473</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -4304,10 +4304,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>-12.75297451019287</v>
+        <v>-1.368064761161804</v>
       </c>
       <c r="B216" t="n">
-        <v>19.32122230529785</v>
+        <v>21.95185279846191</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -4322,10 +4322,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>-8.98880672454834</v>
+        <v>2.594427347183228</v>
       </c>
       <c r="B217" t="n">
-        <v>20.64949607849121</v>
+        <v>20.61270332336426</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -4340,10 +4340,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>-9.193524360656738</v>
+        <v>2.52594518661499</v>
       </c>
       <c r="B218" t="n">
-        <v>20.79353904724121</v>
+        <v>20.88003921508789</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>-9.462079048156738</v>
+        <v>2.475235462188721</v>
       </c>
       <c r="B219" t="n">
-        <v>21.054443359375</v>
+        <v>21.2711353302002</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -4376,10 +4376,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>-9.904117584228516</v>
+        <v>2.289402484893799</v>
       </c>
       <c r="B220" t="n">
-        <v>21.33302879333496</v>
+        <v>21.77630805969238</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -4394,10 +4394,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>-10.39769840240479</v>
+        <v>2.024315595626831</v>
       </c>
       <c r="B221" t="n">
-        <v>21.53292083740234</v>
+        <v>22.249267578125</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -4412,10 +4412,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>-10.84031867980957</v>
+        <v>1.739110946655273</v>
       </c>
       <c r="B222" t="n">
-        <v>21.66157722473145</v>
+        <v>22.63809013366699</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -4430,10 +4430,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>-11.25739765167236</v>
+        <v>1.434937953948975</v>
       </c>
       <c r="B223" t="n">
-        <v>21.72897529602051</v>
+        <v>22.95378684997559</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -4448,10 +4448,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>-11.60657691955566</v>
+        <v>1.144455075263977</v>
       </c>
       <c r="B224" t="n">
-        <v>21.72474098205566</v>
+        <v>23.18190002441406</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -4466,10 +4466,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>-11.31793212890625</v>
+        <v>-1.073407053947449</v>
       </c>
       <c r="B225" t="n">
-        <v>17.95177459716797</v>
+        <v>19.90534591674805</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>-12.14102363586426</v>
+        <v>-1.544287204742432</v>
       </c>
       <c r="B226" t="n">
-        <v>18.23142051696777</v>
+        <v>20.67132759094238</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -4502,10 +4502,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>-12.85345077514648</v>
+        <v>-1.941190600395203</v>
       </c>
       <c r="B227" t="n">
-        <v>18.51904678344727</v>
+        <v>21.36754035949707</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>-9.639986991882324</v>
+        <v>0.9670211672782898</v>
       </c>
       <c r="B228" t="n">
-        <v>18.95090103149414</v>
+        <v>19.63848304748535</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -4538,10 +4538,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>-10.00094509124756</v>
+        <v>0.7361451983451843</v>
       </c>
       <c r="B229" t="n">
-        <v>19.05189895629883</v>
+        <v>19.95290565490723</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -4556,10 +4556,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>-10.58462238311768</v>
+        <v>0.3337867856025696</v>
       </c>
       <c r="B230" t="n">
-        <v>19.17657852172852</v>
+        <v>20.42710304260254</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -4574,10 +4574,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>-10.88729190826416</v>
+        <v>0.1113559231162071</v>
       </c>
       <c r="B231" t="n">
-        <v>19.22473907470703</v>
+        <v>20.66545677185059</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -4592,10 +4592,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>-11.31905555725098</v>
+        <v>-0.1869613975286484</v>
       </c>
       <c r="B232" t="n">
-        <v>19.30064964294434</v>
+        <v>21.01285934448242</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -4610,10 +4610,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>-11.60891246795654</v>
+        <v>-0.3954479992389679</v>
       </c>
       <c r="B233" t="n">
-        <v>19.3557300567627</v>
+        <v>21.2453784942627</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -4628,10 +4628,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>-12.18503284454346</v>
+        <v>-0.7882725596427917</v>
       </c>
       <c r="B234" t="n">
-        <v>19.47030067443848</v>
+        <v>21.7060604095459</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>-12.64414882659912</v>
+        <v>-1.100562691688538</v>
       </c>
       <c r="B235" t="n">
-        <v>19.5605640411377</v>
+        <v>22.0854434967041</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>-9.748234748840332</v>
+        <v>1.928013205528259</v>
       </c>
       <c r="B236" t="n">
-        <v>20.62062072753906</v>
+        <v>21.05059623718262</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -4682,10 +4682,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>-9.899300575256348</v>
+        <v>1.851290345191956</v>
       </c>
       <c r="B237" t="n">
-        <v>20.69484710693359</v>
+        <v>21.21750831604004</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>-10.28169631958008</v>
+        <v>1.6460280418396</v>
       </c>
       <c r="B238" t="n">
-        <v>20.85158157348633</v>
+        <v>21.6058177947998</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -4718,10 +4718,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>-10.70950412750244</v>
+        <v>1.388851761817932</v>
       </c>
       <c r="B239" t="n">
-        <v>20.98773574829102</v>
+        <v>21.98654747009277</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -4736,10 +4736,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>-11.11896419525146</v>
+        <v>1.111421823501587</v>
       </c>
       <c r="B240" t="n">
-        <v>21.09072685241699</v>
+        <v>22.32622718811035</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -4754,10 +4754,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>-11.48816013336182</v>
+        <v>0.8593319654464722</v>
       </c>
       <c r="B241" t="n">
-        <v>21.17550086975098</v>
+        <v>22.63588905334473</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>-11.8453426361084</v>
+        <v>0.6324787139892578</v>
       </c>
       <c r="B242" t="n">
-        <v>21.27541923522949</v>
+        <v>22.95203399658203</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>-7.337215423583984</v>
+        <v>6.644909858703613</v>
       </c>
       <c r="B243" t="n">
-        <v>24.73708343505859</v>
+        <v>22.82789421081543</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>-7.445564746856689</v>
+        <v>6.579557418823242</v>
       </c>
       <c r="B244" t="n">
-        <v>24.7824535369873</v>
+        <v>22.94062805175781</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -4826,10 +4826,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>-7.50753116607666</v>
+        <v>6.536714553833008</v>
       </c>
       <c r="B245" t="n">
-        <v>24.80774879455566</v>
+        <v>23.01158332824707</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -4844,10 +4844,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>-7.577443599700928</v>
+        <v>6.483425140380859</v>
       </c>
       <c r="B246" t="n">
-        <v>24.83650016784668</v>
+        <v>23.09724617004395</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>-7.68584156036377</v>
+        <v>6.400474071502686</v>
       </c>
       <c r="B247" t="n">
-        <v>24.87717247009277</v>
+        <v>23.22583961486816</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -4880,10 +4880,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>-7.740646839141846</v>
+        <v>6.360527992248535</v>
       </c>
       <c r="B248" t="n">
-        <v>24.89640045166016</v>
+        <v>23.28437614440918</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>-7.819275379180908</v>
+        <v>6.306781768798828</v>
       </c>
       <c r="B249" t="n">
-        <v>24.9221363067627</v>
+        <v>23.36066055297852</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -4916,10 +4916,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>-0.6887115240097046</v>
+        <v>3.991013526916504</v>
       </c>
       <c r="B250" t="n">
-        <v>11.36030769348145</v>
+        <v>7.788486480712891</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>-1.677323460578918</v>
+        <v>2.995531320571899</v>
       </c>
       <c r="B251" t="n">
-        <v>10.9833345413208</v>
+        <v>7.951239109039307</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -4952,10 +4952,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>-0.7503224015235901</v>
+        <v>3.889182567596436</v>
       </c>
       <c r="B252" t="n">
-        <v>11.29802703857422</v>
+        <v>7.789144039154053</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -4970,10 +4970,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>-1.517284870147705</v>
+        <v>2.89208459854126</v>
       </c>
       <c r="B253" t="n">
-        <v>10.88016033172607</v>
+        <v>8.210057258605957</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>-0.7501986622810364</v>
+        <v>3.876963138580322</v>
       </c>
       <c r="B254" t="n">
-        <v>11.29732131958008</v>
+        <v>7.77998161315918</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>-1.507214546203613</v>
+        <v>2.991706848144531</v>
       </c>
       <c r="B255" t="n">
-        <v>10.88034820556641</v>
+        <v>7.95242977142334</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -5024,10 +5024,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>-0.851190447807312</v>
+        <v>3.633963346481323</v>
       </c>
       <c r="B256" t="n">
-        <v>11.16163063049316</v>
+        <v>7.723230838775635</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -5042,10 +5042,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>-1.672833919525146</v>
+        <v>2.889243364334106</v>
       </c>
       <c r="B257" t="n">
-        <v>10.97505950927734</v>
+        <v>8.216567039489746</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>-0.03772504255175591</v>
+        <v>3.913556098937988</v>
       </c>
       <c r="B258" t="n">
-        <v>10.60055160522461</v>
+        <v>6.725759983062744</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>-0.9955064058303833</v>
+        <v>2.87479829788208</v>
       </c>
       <c r="B259" t="n">
-        <v>10.18084335327148</v>
+        <v>7.074362277984619</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -5096,10 +5096,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>-0.06849315017461777</v>
+        <v>3.870599746704102</v>
       </c>
       <c r="B260" t="n">
-        <v>10.57778549194336</v>
+        <v>6.729999542236328</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>-0.9955609440803528</v>
+        <v>2.87470555305481</v>
       </c>
       <c r="B261" t="n">
-        <v>10.18051147460938</v>
+        <v>7.074264526367188</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -5132,10 +5132,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>0.5226173996925354</v>
+        <v>5.669510364532471</v>
       </c>
       <c r="B262" t="n">
-        <v>12.37045669555664</v>
+        <v>7.729852199554443</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>-1.21593189239502</v>
+        <v>3.713044404983521</v>
       </c>
       <c r="B263" t="n">
-        <v>11.60481357574463</v>
+        <v>8.359170913696289</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -5168,10 +5168,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>-1.806403636932373</v>
+        <v>3.126978397369385</v>
       </c>
       <c r="B264" t="n">
-        <v>11.40928840637207</v>
+        <v>8.617980003356934</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -5186,10 +5186,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>0.5089818835258484</v>
+        <v>5.646630764007568</v>
       </c>
       <c r="B265" t="n">
-        <v>12.354811668396</v>
+        <v>7.725980758666992</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>-1.262069344520569</v>
+        <v>3.66991925239563</v>
       </c>
       <c r="B266" t="n">
-        <v>11.59403896331787</v>
+        <v>8.381377220153809</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -5222,10 +5222,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>0.8749295473098755</v>
+        <v>6.948223114013672</v>
       </c>
       <c r="B267" t="n">
-        <v>13.7201566696167</v>
+        <v>8.507998466491699</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -5240,10 +5240,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>0.2939725816249847</v>
+        <v>6.179277420043945</v>
       </c>
       <c r="B268" t="n">
-        <v>13.31517124176025</v>
+        <v>8.607211112976074</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -5258,10 +5258,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>-0.7329310774803162</v>
+        <v>4.892621040344238</v>
       </c>
       <c r="B269" t="n">
-        <v>12.69105243682861</v>
+        <v>8.843029022216797</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -5276,10 +5276,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>-1.408223390579224</v>
+        <v>4.142390727996826</v>
       </c>
       <c r="B270" t="n">
-        <v>12.36912822723389</v>
+        <v>9.071297645568848</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -5294,10 +5294,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>0.8795664310455322</v>
+        <v>6.954499244689941</v>
       </c>
       <c r="B271" t="n">
-        <v>13.72366142272949</v>
+        <v>8.507291793823242</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -5312,10 +5312,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>0.3179139196872711</v>
+        <v>6.209329128265381</v>
       </c>
       <c r="B272" t="n">
-        <v>13.32837867736816</v>
+        <v>8.600215911865234</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>-0.6917421221733093</v>
+        <v>4.944117546081543</v>
       </c>
       <c r="B273" t="n">
-        <v>12.71466732025146</v>
+        <v>8.83205509185791</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -5348,10 +5348,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>-2.518523693084717</v>
+        <v>3.449220418930054</v>
       </c>
       <c r="B274" t="n">
-        <v>12.69477081298828</v>
+        <v>10.11020278930664</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -5366,10 +5366,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>-2.733034133911133</v>
+        <v>3.171115398406982</v>
       </c>
       <c r="B275" t="n">
-        <v>12.56933784484863</v>
+        <v>10.17754745483398</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -5384,10 +5384,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>-2.518523693084717</v>
+        <v>3.449058055877686</v>
       </c>
       <c r="B276" t="n">
-        <v>12.69477081298828</v>
+        <v>10.11020946502686</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>-2.733026504516602</v>
+        <v>3.170788049697876</v>
       </c>
       <c r="B277" t="n">
-        <v>12.56918525695801</v>
+        <v>10.17657947540283</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -5420,10 +5420,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>-0.1078649088740349</v>
+        <v>6.529178619384766</v>
       </c>
       <c r="B278" t="n">
-        <v>14.33583831787109</v>
+        <v>9.722629547119141</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -5438,10 +5438,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>-0.5557107329368591</v>
+        <v>6.119112014770508</v>
       </c>
       <c r="B279" t="n">
-        <v>14.26247024536133</v>
+        <v>9.969338417053223</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -5456,10 +5456,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>-1.097604990005493</v>
+        <v>5.589765071868896</v>
       </c>
       <c r="B280" t="n">
-        <v>14.1176872253418</v>
+        <v>10.23804092407227</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -5474,10 +5474,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>-1.661147952079773</v>
+        <v>4.964473247528076</v>
       </c>
       <c r="B281" t="n">
-        <v>13.86875152587891</v>
+        <v>10.44294261932373</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>-2.123514652252197</v>
+        <v>4.417602062225342</v>
       </c>
       <c r="B282" t="n">
-        <v>13.6290283203125</v>
+        <v>10.54312324523926</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>-2.503813743591309</v>
+        <v>4.105400085449219</v>
       </c>
       <c r="B283" t="n">
-        <v>13.62364673614502</v>
+        <v>10.82958316802979</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -5528,10 +5528,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>-1.097603678703308</v>
+        <v>5.589467525482178</v>
       </c>
       <c r="B284" t="n">
-        <v>14.11768245697021</v>
+        <v>10.23591423034668</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -5546,10 +5546,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>-1.635286450386047</v>
+        <v>4.994801998138428</v>
       </c>
       <c r="B285" t="n">
-        <v>13.8811502456665</v>
+        <v>10.435546875</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -5564,10 +5564,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>-2.122880458831787</v>
+        <v>4.418939590454102</v>
       </c>
       <c r="B286" t="n">
-        <v>13.62668514251709</v>
+        <v>10.54139995574951</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -5582,10 +5582,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>-2.503813743591309</v>
+        <v>4.105404853820801</v>
       </c>
       <c r="B287" t="n">
-        <v>13.6236457824707</v>
+        <v>10.8295726776123</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -5600,10 +5600,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>18.25500869750977</v>
+        <v>14.24285125732422</v>
       </c>
       <c r="B288" t="n">
-        <v>6.146985054016113</v>
+        <v>1.255150675773621</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -5618,10 +5618,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>18.08826446533203</v>
+        <v>13.97216606140137</v>
       </c>
       <c r="B289" t="n">
-        <v>5.806113719940186</v>
+        <v>0.9478418827056885</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -5636,10 +5636,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>17.96990013122559</v>
+        <v>13.77176666259766</v>
       </c>
       <c r="B290" t="n">
-        <v>5.589501857757568</v>
+        <v>0.7545265555381775</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -5654,10 +5654,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>18.00118827819824</v>
+        <v>13.79754447937012</v>
       </c>
       <c r="B291" t="n">
-        <v>5.564857959747314</v>
+        <v>0.7096304893493652</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -5672,10 +5672,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>18.95085525512695</v>
+        <v>14.87757682800293</v>
       </c>
       <c r="B292" t="n">
-        <v>5.896884918212891</v>
+        <v>0.7379219532012939</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -5690,10 +5690,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>18.7702579498291</v>
+        <v>14.59676265716553</v>
       </c>
       <c r="B293" t="n">
-        <v>5.661839485168457</v>
+        <v>0.5065195560455322</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -5708,10 +5708,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>16.77060890197754</v>
+        <v>12.05522155761719</v>
       </c>
       <c r="B294" t="n">
-        <v>4.028351783752441</v>
+        <v>-0.2434093356132507</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>20.48061752319336</v>
+        <v>16.40094184875488</v>
       </c>
       <c r="B295" t="n">
-        <v>5.411459922790527</v>
+        <v>-0.2228579968214035</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>20.3879451751709</v>
+        <v>16.21595764160156</v>
       </c>
       <c r="B296" t="n">
-        <v>5.135116100311279</v>
+        <v>-0.4766258299350739</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -5762,10 +5762,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>20.26937294006348</v>
+        <v>15.98031330108643</v>
       </c>
       <c r="B297" t="n">
-        <v>4.808845996856689</v>
+        <v>-0.7799856066703796</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>20.21379089355469</v>
+        <v>15.86643695831299</v>
       </c>
       <c r="B298" t="n">
-        <v>4.659933090209961</v>
+        <v>-0.927105724811554</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -5798,10 +5798,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>18.96858024597168</v>
+        <v>14.71804618835449</v>
       </c>
       <c r="B299" t="n">
-        <v>4.860283851623535</v>
+        <v>-0.2642561793327332</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -5816,10 +5816,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>18.86307144165039</v>
+        <v>14.50573062896729</v>
       </c>
       <c r="B300" t="n">
-        <v>4.605767250061035</v>
+        <v>-0.5434461832046509</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>19.62135696411133</v>
+        <v>15.62150764465332</v>
       </c>
       <c r="B301" t="n">
-        <v>5.709695816040039</v>
+        <v>0.4146859049797058</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>19.36425399780273</v>
+        <v>15.25471782684326</v>
       </c>
       <c r="B302" t="n">
-        <v>5.274442672729492</v>
+        <v>0.06216484680771828</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -5870,10 +5870,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>19.09002876281738</v>
+        <v>14.84217357635498</v>
       </c>
       <c r="B303" t="n">
-        <v>4.858737945556641</v>
+        <v>-0.295261949300766</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -5888,10 +5888,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>18.9831371307373</v>
+        <v>14.61560535430908</v>
       </c>
       <c r="B304" t="n">
-        <v>4.558917999267578</v>
+        <v>-0.6306458115577698</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -5906,10 +5906,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>19.76457786560059</v>
+        <v>15.75130271911621</v>
       </c>
       <c r="B305" t="n">
-        <v>5.653432369232178</v>
+        <v>0.2827726602554321</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -5924,10 +5924,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>19.55167961120605</v>
+        <v>15.42974090576172</v>
       </c>
       <c r="B306" t="n">
-        <v>5.218671321868896</v>
+        <v>-0.0799819678068161</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -5942,10 +5942,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>19.42911911010742</v>
+        <v>15.13911056518555</v>
       </c>
       <c r="B307" t="n">
-        <v>4.723190784454346</v>
+        <v>-0.5301722288131714</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -5960,10 +5960,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>19.34390640258789</v>
+        <v>14.96301364898682</v>
       </c>
       <c r="B308" t="n">
-        <v>4.499111175537109</v>
+        <v>-0.7869666814804077</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -5978,10 +5978,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>17.76786041259766</v>
+        <v>13.16399574279785</v>
       </c>
       <c r="B309" t="n">
-        <v>2.248438835144043</v>
+        <v>-3.169505596160889</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>17.75507736206055</v>
+        <v>13.14135456085205</v>
       </c>
       <c r="B310" t="n">
-        <v>2.237857103347778</v>
+        <v>-3.185800790786743</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -6014,10 +6014,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>20.44597434997559</v>
+        <v>15.44304084777832</v>
       </c>
       <c r="B311" t="n">
-        <v>1.500062823295593</v>
+        <v>-3.437681436538696</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>20.01267433166504</v>
+        <v>15.11554527282715</v>
       </c>
       <c r="B312" t="n">
-        <v>1.925860285758972</v>
+        <v>-3.687706708908081</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -6050,10 +6050,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>19.56930923461914</v>
+        <v>14.80424022674561</v>
       </c>
       <c r="B313" t="n">
-        <v>1.970597982406616</v>
+        <v>-4.039418697357178</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -6068,10 +6068,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>19.17014503479004</v>
+        <v>14.58711051940918</v>
       </c>
       <c r="B314" t="n">
-        <v>1.715916156768799</v>
+        <v>-4.426538467407227</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -6086,10 +6086,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>20.0405158996582</v>
+        <v>15.47941875457764</v>
       </c>
       <c r="B315" t="n">
-        <v>1.607809543609619</v>
+        <v>-4.008254051208496</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -6104,10 +6104,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>20.44597434997559</v>
+        <v>15.44304084777832</v>
       </c>
       <c r="B316" t="n">
-        <v>1.500062823295593</v>
+        <v>-3.437681436538696</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -6122,10 +6122,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>20.01267433166504</v>
+        <v>15.11554527282715</v>
       </c>
       <c r="B317" t="n">
-        <v>1.925860285758972</v>
+        <v>-3.687706708908081</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -6140,10 +6140,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>19.56930923461914</v>
+        <v>14.80424022674561</v>
       </c>
       <c r="B318" t="n">
-        <v>1.970597982406616</v>
+        <v>-4.039418697357178</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -6158,10 +6158,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>19.17014503479004</v>
+        <v>14.58711051940918</v>
       </c>
       <c r="B319" t="n">
-        <v>1.715916156768799</v>
+        <v>-4.426538467407227</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -6176,10 +6176,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>20.02029418945312</v>
+        <v>15.65969562530518</v>
       </c>
       <c r="B320" t="n">
-        <v>1.22327184677124</v>
+        <v>-4.287337779998779</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -6194,10 +6194,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>19.60843467712402</v>
+        <v>15.41976737976074</v>
       </c>
       <c r="B321" t="n">
-        <v>1.25028133392334</v>
+        <v>-4.54813289642334</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -6212,10 +6212,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>19.24350166320801</v>
+        <v>15.10507869720459</v>
       </c>
       <c r="B322" t="n">
-        <v>1.252117991447449</v>
+        <v>-4.764035224914551</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -6230,10 +6230,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>22.36137008666992</v>
+        <v>17.83325386047363</v>
       </c>
       <c r="B323" t="n">
-        <v>2.472624063491821</v>
+        <v>-2.629984855651855</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -6248,10 +6248,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>22.15278434753418</v>
+        <v>17.79787445068359</v>
       </c>
       <c r="B324" t="n">
-        <v>2.755106449127197</v>
+        <v>-3.004127264022827</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -6266,10 +6266,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>21.93175506591797</v>
+        <v>17.76683044433594</v>
       </c>
       <c r="B325" t="n">
-        <v>3.036796569824219</v>
+        <v>-3.382549524307251</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -6284,10 +6284,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>21.73201179504395</v>
+        <v>17.69556999206543</v>
       </c>
       <c r="B326" t="n">
-        <v>3.209231376647949</v>
+        <v>-3.708144426345825</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -6302,10 +6302,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>21.66458129882812</v>
+        <v>17.63849639892578</v>
       </c>
       <c r="B327" t="n">
-        <v>3.235963106155396</v>
+        <v>-3.810402393341064</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -6320,10 +6320,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>22.09624862670898</v>
+        <v>17.42828178405762</v>
       </c>
       <c r="B328" t="n">
-        <v>2.165718078613281</v>
+        <v>-2.556251287460327</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -6338,10 +6338,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>21.80469703674316</v>
+        <v>17.2305793762207</v>
       </c>
       <c r="B329" t="n">
-        <v>2.357400178909302</v>
+        <v>-2.884266376495361</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -6356,10 +6356,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>21.54266738891602</v>
+        <v>17.16024208068848</v>
       </c>
       <c r="B330" t="n">
-        <v>2.61612868309021</v>
+        <v>-3.21599268913269</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -6374,10 +6374,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>21.36244964599609</v>
+        <v>17.19127655029297</v>
       </c>
       <c r="B331" t="n">
-        <v>2.864570379257202</v>
+        <v>-3.545936822891235</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -6392,10 +6392,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>21.31389808654785</v>
+        <v>17.21448516845703</v>
       </c>
       <c r="B332" t="n">
-        <v>2.916392803192139</v>
+        <v>-3.684395313262939</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>19.56494522094727</v>
+        <v>14.55195713043213</v>
       </c>
       <c r="B333" t="n">
-        <v>-1.432847261428833</v>
+        <v>-6.551047325134277</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -6428,10 +6428,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>19.52445030212402</v>
+        <v>14.41812133789062</v>
       </c>
       <c r="B334" t="n">
-        <v>-1.617079973220825</v>
+        <v>-6.743359565734863</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -6446,10 +6446,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>19.48991966247559</v>
+        <v>14.26927947998047</v>
       </c>
       <c r="B335" t="n">
-        <v>-1.820253968238831</v>
+        <v>-6.976906299591064</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -6464,10 +6464,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>19.4493408203125</v>
+        <v>14.13959789276123</v>
       </c>
       <c r="B336" t="n">
-        <v>-1.999878644943237</v>
+        <v>-7.207083225250244</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>19.52445030212402</v>
+        <v>14.41812133789062</v>
       </c>
       <c r="B337" t="n">
-        <v>-1.617079973220825</v>
+        <v>-6.743359565734863</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -6500,10 +6500,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>19.48991966247559</v>
+        <v>14.26927947998047</v>
       </c>
       <c r="B338" t="n">
-        <v>-1.820253968238831</v>
+        <v>-6.976906299591064</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -6518,10 +6518,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>19.4493408203125</v>
+        <v>14.13959789276123</v>
       </c>
       <c r="B339" t="n">
-        <v>-1.999878644943237</v>
+        <v>-7.207083225250244</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -6536,10 +6536,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>20.55524635314941</v>
+        <v>15.63244819641113</v>
       </c>
       <c r="B340" t="n">
-        <v>-1.642420411109924</v>
+        <v>-7.197498321533203</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -6554,10 +6554,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>20.6375560760498</v>
+        <v>15.78785037994385</v>
       </c>
       <c r="B341" t="n">
-        <v>-1.536324024200439</v>
+        <v>-7.076479434967041</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -6572,10 +6572,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>20.57753372192383</v>
+        <v>15.6686954498291</v>
       </c>
       <c r="B342" t="n">
-        <v>-1.628667593002319</v>
+        <v>-7.181406497955322</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
